--- a/artfynd/A 35828-2024 artfynd.xlsx
+++ b/artfynd/A 35828-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83272109</v>
+        <v>61538304</v>
       </c>
       <c r="B2" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109866</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>220228</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,24 +703,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tavelhult 1:3&gt;1, Vg</t>
+          <t>ängsrest vid liden upp till Tavelhult, Utvängstorp, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435408.1595372368</v>
+        <v>435428</v>
       </c>
       <c r="R2" t="n">
-        <v>6433209.616066108</v>
+        <v>6433226</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,29 +738,19 @@
           <t>Utvängstorp</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>196D6BDC-9702-4EA3-8111-188419AB2739</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-06-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-06-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1 ex blommade om; också fin bladrosett</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,31 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Jörgen Grahn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson, Marie Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>117279400</v>
       </c>
       <c r="B3" t="n">
-        <v>108703</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,6 +871,116 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>83272109</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tavelhult 1:3&gt;1, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>435408</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6433210</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Utvängstorp</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>196D6BDC-9702-4EA3-8111-188419AB2739</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2007-06-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2007-06-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson, Marie Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35828-2024 artfynd.xlsx
+++ b/artfynd/A 35828-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61538304</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117279400</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,8 +996,18 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83272109</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>